--- a/InputData/trans/BCDTRtSY/BAU Cargo Dist Transported Relative to Start Yr.xlsx
+++ b/InputData/trans/BCDTRtSY/BAU Cargo Dist Transported Relative to Start Yr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10512"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\trans\BCDTRtSY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lawrenceiu/Desktop/eps-HK-3.4.9-working/InputData/trans/BCDTRtSY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_F38115EF335BB3F3DFF8AD42D1B3136DDB95550E" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{C493DB9E-4B6F-4DD2-B7A5-9EDF7A32E6F1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F41E91-8874-A94D-8E9D-3A72F24DDFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="742" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15580" yWindow="4500" windowWidth="27000" windowHeight="16720" tabRatio="742" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,17 @@
     <definedName name="ti_tbl_69" localSheetId="4">#REF!</definedName>
     <definedName name="ti_tbl_69">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -252,26 +257,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="###0.00_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0000000_);_(* \(#,##0.0000000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00000000000_);_(* \(#,##0.00000000000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="###0.00_)"/>
+    <numFmt numFmtId="178" formatCode="#,##0_)"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0000000_);_(* \(#,##0.0000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0.00000000000_);_(* \(#,##0.00000000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="181" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -279,7 +284,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -501,8 +506,15 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -919,22 +931,22 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="8">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="8">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1066,7 +1078,7 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="8">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyNumberFormat="0">
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" applyNumberFormat="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
@@ -1113,7 +1125,7 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1126,22 +1138,21 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1169,6 +1180,8 @@
     <cellStyle name="60% - Accent4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="60% - Accent5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="60% - Accent6 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="153" builtinId="8"/>
     <cellStyle name="Accent1 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
     <cellStyle name="Accent2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
     <cellStyle name="Accent3 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
@@ -1219,12 +1232,10 @@
     <cellStyle name="Hed Top" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
     <cellStyle name="Hed Top - SECTION" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
     <cellStyle name="Hed Top_3-new4" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="Hyperlink" xfId="153" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
     <cellStyle name="Input 2" xfId="73" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
     <cellStyle name="Linked Cell 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
     <cellStyle name="Neutral 2" xfId="75" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="76" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
     <cellStyle name="Normal 11" xfId="77" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
@@ -1320,7 +1331,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Rail shipments 93-97"/>
@@ -1401,9 +1412,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1441,9 +1452,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1476,26 +1487,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1528,26 +1522,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1725,7 +1702,7 @@
     <tabColor rgb="FFC6E0B4"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
@@ -1763,6 +1740,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="41" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
@@ -1774,9 +1752,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3955775-2F14-4E2D-AD91-38954BF95459}">
   <dimension ref="A1:BK107"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5402,6 +5380,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5409,124 +5388,126 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="37" width="16.28515625" style="2" customWidth="1"/>
+    <col min="3" max="37" width="16.19921875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="11" customFormat="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:37">
+      <c r="A1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12">
+      <c r="B1" s="11">
         <v>2017</v>
       </c>
-      <c r="C1" s="12">
+      <c r="C1" s="11">
         <v>2018</v>
       </c>
-      <c r="D1" s="12">
+      <c r="D1" s="11">
         <v>2019</v>
       </c>
-      <c r="E1" s="12">
+      <c r="E1" s="11">
         <v>2020</v>
       </c>
-      <c r="F1" s="12">
+      <c r="F1" s="11">
         <v>2021</v>
       </c>
-      <c r="G1" s="12">
+      <c r="G1" s="11">
         <v>2022</v>
       </c>
-      <c r="H1" s="12">
+      <c r="H1" s="11">
         <v>2023</v>
       </c>
-      <c r="I1" s="12">
+      <c r="I1" s="11">
         <v>2024</v>
       </c>
-      <c r="J1" s="12">
+      <c r="J1" s="11">
         <v>2025</v>
       </c>
-      <c r="K1" s="12">
+      <c r="K1" s="11">
         <v>2026</v>
       </c>
-      <c r="L1" s="12">
+      <c r="L1" s="11">
         <v>2027</v>
       </c>
-      <c r="M1" s="12">
+      <c r="M1" s="11">
         <v>2028</v>
       </c>
-      <c r="N1" s="12">
+      <c r="N1" s="11">
         <v>2029</v>
       </c>
-      <c r="O1" s="12">
+      <c r="O1" s="11">
         <v>2030</v>
       </c>
-      <c r="P1" s="12">
+      <c r="P1" s="11">
         <v>2031</v>
       </c>
-      <c r="Q1" s="12">
+      <c r="Q1" s="11">
         <v>2032</v>
       </c>
-      <c r="R1" s="12">
+      <c r="R1" s="11">
         <v>2033</v>
       </c>
-      <c r="S1" s="12">
+      <c r="S1" s="11">
         <v>2034</v>
       </c>
-      <c r="T1" s="12">
+      <c r="T1" s="11">
         <v>2035</v>
       </c>
-      <c r="U1" s="12">
+      <c r="U1" s="11">
         <v>2036</v>
       </c>
-      <c r="V1" s="12">
+      <c r="V1" s="11">
         <v>2037</v>
       </c>
-      <c r="W1" s="12">
+      <c r="W1" s="11">
         <v>2038</v>
       </c>
-      <c r="X1" s="12">
+      <c r="X1" s="11">
         <v>2039</v>
       </c>
-      <c r="Y1" s="12">
+      <c r="Y1" s="11">
         <v>2040</v>
       </c>
-      <c r="Z1" s="12">
+      <c r="Z1" s="11">
         <v>2041</v>
       </c>
-      <c r="AA1" s="12">
+      <c r="AA1" s="11">
         <v>2042</v>
       </c>
-      <c r="AB1" s="12">
+      <c r="AB1" s="11">
         <v>2043</v>
       </c>
-      <c r="AC1" s="12">
+      <c r="AC1" s="11">
         <v>2044</v>
       </c>
-      <c r="AD1" s="12">
+      <c r="AD1" s="11">
         <v>2045</v>
       </c>
-      <c r="AE1" s="12">
+      <c r="AE1" s="11">
         <v>2046</v>
       </c>
-      <c r="AF1" s="12">
+      <c r="AF1" s="11">
         <v>2047</v>
       </c>
-      <c r="AG1" s="12">
+      <c r="AG1" s="11">
         <v>2048</v>
       </c>
-      <c r="AH1" s="12">
+      <c r="AH1" s="11">
         <v>2049</v>
       </c>
-      <c r="AI1" s="12">
+      <c r="AI1" s="11">
         <v>2050</v>
       </c>
+      <c r="AJ1"/>
+      <c r="AK1"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>7389500</v>
       </c>
       <c r="C2" s="4">
@@ -5632,7 +5613,7 @@
       <c r="AK2"/>
     </row>
     <row r="3" spans="1:37">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -5741,7 +5722,7 @@
       <c r="AK3"/>
     </row>
     <row r="4" spans="1:37">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>57</v>
       </c>
       <c r="B4" s="6"/>
@@ -5890,6 +5871,7 @@
       <c r="C10" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5899,1002 +5881,893 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AL14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AH14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="38" width="10.140625" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" customWidth="1"/>
+    <col min="2" max="34" width="10.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:34">
       <c r="B1">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C1">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="D1">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="E1">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="F1">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G1">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="H1">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="I1">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="J1">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="K1">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="L1">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="M1">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="N1">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="O1">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="P1">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="Q1">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="R1">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="S1">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="T1">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="U1">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="V1">
-        <v>2036</v>
+        <v>2040</v>
       </c>
       <c r="W1">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="X1">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="Y1">
-        <v>2039</v>
+        <v>2043</v>
       </c>
       <c r="Z1">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="AA1">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="AB1">
-        <v>2042</v>
+        <v>2046</v>
       </c>
       <c r="AC1">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="AD1">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="AE1">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="AF1">
-        <v>2046</v>
-      </c>
-      <c r="AG1">
-        <v>2047</v>
-      </c>
-      <c r="AH1">
-        <v>2048</v>
-      </c>
-      <c r="AI1">
-        <v>2049</v>
-      </c>
-      <c r="AJ1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:34">
       <c r="A2" t="s">
         <v>58</v>
       </c>
       <c r="B2">
-        <f>'Lawrence''s projections'!N$21/'Lawrence''s projections'!$N$21</f>
+        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$R$21</f>
         <v>1</v>
       </c>
       <c r="C2">
-        <f>'Lawrence''s projections'!O$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0227053788099791</v>
+        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0185734972871554</v>
       </c>
       <c r="D2">
-        <f>'Lawrence''s projections'!P$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0452319067405111</v>
+        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0366094241084758</v>
       </c>
       <c r="E2">
-        <f>'Lawrence''s projections'!Q$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0668176091706185</v>
+        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0540381204293101</v>
       </c>
       <c r="F2">
-        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0881844844019679</v>
+        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0704910645018531</v>
       </c>
       <c r="G2">
-        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1083958759709325</v>
+        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0862172536972476</v>
       </c>
       <c r="H2">
-        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1280222916997029</v>
+        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1010910619100174</v>
       </c>
       <c r="I2">
-        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1469879286193883</v>
+        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1153205331525904</v>
       </c>
       <c r="J2">
-        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1648917670818628</v>
+        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1292985133114011</v>
       </c>
       <c r="K2">
-        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1820047621630612</v>
+        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1428470896719243</v>
       </c>
       <c r="L2">
-        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1981902094841677</v>
+        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1557680882483976</v>
       </c>
       <c r="M2">
-        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2136744993115798</v>
+        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1681927379592973</v>
       </c>
       <c r="N2">
-        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2288851204436759</v>
+        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1801572515255192</v>
       </c>
       <c r="O2">
-        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2436284710249326</v>
+        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1917550324649424</v>
       </c>
       <c r="P2">
-        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2576889011988308</v>
+        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2027556833967945</v>
       </c>
       <c r="Q2">
-        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2712092122383614</v>
+        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2130009951676641</v>
       </c>
       <c r="R2">
-        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2842288102645407</v>
+        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2225748016844051</v>
       </c>
       <c r="S2">
-        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.296849335536314</v>
+        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2314569249479494</v>
       </c>
       <c r="T2">
-        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3088200731986774</v>
+        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2395815736087508</v>
       </c>
       <c r="U2">
-        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3199688625055988</v>
+        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2468376869604936</v>
       </c>
       <c r="V2">
-        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3303869302137827</v>
+        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2533299712929726</v>
       </c>
       <c r="W2">
-        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3400523189377174</v>
+        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2589919188817484</v>
       </c>
       <c r="X2">
-        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3488934355516187</v>
+        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2638813382323244</v>
       </c>
       <c r="Y2">
-        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.356789425518047</v>
+        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2681800631215496</v>
       </c>
       <c r="Z2">
-        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3638542285969768</v>
+        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2718428653863023</v>
       </c>
       <c r="AA2">
-        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3700154721145799</v>
+        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2747902811690834</v>
       </c>
       <c r="AB2">
-        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3753360623896114</v>
+        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.277067223642631</v>
       </c>
       <c r="AC2">
-        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3800138681167788</v>
+        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2785593661591077</v>
       </c>
       <c r="AD2">
-        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3839996727107149</v>
+        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2794472919117685</v>
       </c>
       <c r="AE2">
-        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3872070048346188</v>
+        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2796273844678205</v>
       </c>
       <c r="AF2">
-        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3896847383062092</v>
-      </c>
-      <c r="AG2">
-        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3913084646411555</v>
-      </c>
-      <c r="AH2">
-        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392274691668502</v>
-      </c>
-      <c r="AI2">
-        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392470665593754</v>
-      </c>
-      <c r="AJ2">
-        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3919192618611231</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38">
+        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2791206654872296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3" t="s">
         <v>59</v>
       </c>
       <c r="B3">
-        <f>'Lawrence''s projections'!N$21/'Lawrence''s projections'!$N$21</f>
+        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$R$21</f>
         <v>1</v>
       </c>
       <c r="C3">
-        <f>'Lawrence''s projections'!O$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0227053788099791</v>
+        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0185734972871554</v>
       </c>
       <c r="D3">
-        <f>'Lawrence''s projections'!P$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0452319067405111</v>
+        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0366094241084758</v>
       </c>
       <c r="E3">
-        <f>'Lawrence''s projections'!Q$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0668176091706185</v>
+        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0540381204293101</v>
       </c>
       <c r="F3">
-        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0881844844019679</v>
+        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0704910645018531</v>
       </c>
       <c r="G3">
-        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1083958759709325</v>
+        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0862172536972476</v>
       </c>
       <c r="H3">
-        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1280222916997029</v>
+        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1010910619100174</v>
       </c>
       <c r="I3">
-        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1469879286193883</v>
+        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1153205331525904</v>
       </c>
       <c r="J3">
-        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1648917670818628</v>
+        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1292985133114011</v>
       </c>
       <c r="K3">
-        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1820047621630612</v>
+        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1428470896719243</v>
       </c>
       <c r="L3">
-        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1981902094841677</v>
+        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1557680882483976</v>
       </c>
       <c r="M3">
-        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2136744993115798</v>
+        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1681927379592973</v>
       </c>
       <c r="N3">
-        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2288851204436759</v>
+        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1801572515255192</v>
       </c>
       <c r="O3">
-        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2436284710249326</v>
+        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1917550324649424</v>
       </c>
       <c r="P3">
-        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2576889011988308</v>
+        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2027556833967945</v>
       </c>
       <c r="Q3">
-        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2712092122383614</v>
+        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2130009951676641</v>
       </c>
       <c r="R3">
-        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2842288102645407</v>
+        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2225748016844051</v>
       </c>
       <c r="S3">
-        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.296849335536314</v>
+        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2314569249479494</v>
       </c>
       <c r="T3">
-        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3088200731986774</v>
+        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2395815736087508</v>
       </c>
       <c r="U3">
-        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3199688625055988</v>
+        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2468376869604936</v>
       </c>
       <c r="V3">
-        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3303869302137827</v>
+        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2533299712929726</v>
       </c>
       <c r="W3">
-        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3400523189377174</v>
+        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2589919188817484</v>
       </c>
       <c r="X3">
-        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3488934355516187</v>
+        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2638813382323244</v>
       </c>
       <c r="Y3">
-        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.356789425518047</v>
+        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2681800631215496</v>
       </c>
       <c r="Z3">
-        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3638542285969768</v>
+        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2718428653863023</v>
       </c>
       <c r="AA3">
-        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3700154721145799</v>
+        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2747902811690834</v>
       </c>
       <c r="AB3">
-        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3753360623896114</v>
+        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.277067223642631</v>
       </c>
       <c r="AC3">
-        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3800138681167788</v>
+        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2785593661591077</v>
       </c>
       <c r="AD3">
-        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3839996727107149</v>
+        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2794472919117685</v>
       </c>
       <c r="AE3">
-        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3872070048346188</v>
+        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2796273844678205</v>
       </c>
       <c r="AF3">
-        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3896847383062092</v>
-      </c>
-      <c r="AG3">
-        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3913084646411555</v>
-      </c>
-      <c r="AH3">
-        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392274691668502</v>
-      </c>
-      <c r="AI3">
-        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392470665593754</v>
-      </c>
-      <c r="AJ3">
-        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3919192618611231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38">
+        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2791206654872296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34">
       <c r="A4" t="s">
         <v>60</v>
       </c>
       <c r="B4">
-        <f>'Lawrence''s projections'!N$21/'Lawrence''s projections'!$N$21</f>
+        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$R$21</f>
         <v>1</v>
       </c>
       <c r="C4">
-        <f>'Lawrence''s projections'!O$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0227053788099791</v>
+        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0185734972871554</v>
       </c>
       <c r="D4">
-        <f>'Lawrence''s projections'!P$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0452319067405111</v>
+        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0366094241084758</v>
       </c>
       <c r="E4">
-        <f>'Lawrence''s projections'!Q$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0668176091706185</v>
+        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0540381204293101</v>
       </c>
       <c r="F4">
-        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0881844844019679</v>
+        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0704910645018531</v>
       </c>
       <c r="G4">
-        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1083958759709325</v>
+        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0862172536972476</v>
       </c>
       <c r="H4">
-        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1280222916997029</v>
+        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1010910619100174</v>
       </c>
       <c r="I4">
-        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1469879286193883</v>
+        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1153205331525904</v>
       </c>
       <c r="J4">
-        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1648917670818628</v>
+        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1292985133114011</v>
       </c>
       <c r="K4">
-        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1820047621630612</v>
+        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1428470896719243</v>
       </c>
       <c r="L4">
-        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1981902094841677</v>
+        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1557680882483976</v>
       </c>
       <c r="M4">
-        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2136744993115798</v>
+        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1681927379592973</v>
       </c>
       <c r="N4">
-        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2288851204436759</v>
+        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1801572515255192</v>
       </c>
       <c r="O4">
-        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2436284710249326</v>
+        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1917550324649424</v>
       </c>
       <c r="P4">
-        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2576889011988308</v>
+        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2027556833967945</v>
       </c>
       <c r="Q4">
-        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2712092122383614</v>
+        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2130009951676641</v>
       </c>
       <c r="R4">
-        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2842288102645407</v>
+        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2225748016844051</v>
       </c>
       <c r="S4">
-        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.296849335536314</v>
+        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2314569249479494</v>
       </c>
       <c r="T4">
-        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3088200731986774</v>
+        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2395815736087508</v>
       </c>
       <c r="U4">
-        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3199688625055988</v>
+        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2468376869604936</v>
       </c>
       <c r="V4">
-        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3303869302137827</v>
+        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2533299712929726</v>
       </c>
       <c r="W4">
-        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3400523189377174</v>
+        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2589919188817484</v>
       </c>
       <c r="X4">
-        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3488934355516187</v>
+        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2638813382323244</v>
       </c>
       <c r="Y4">
-        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.356789425518047</v>
+        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2681800631215496</v>
       </c>
       <c r="Z4">
-        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3638542285969768</v>
+        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2718428653863023</v>
       </c>
       <c r="AA4">
-        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3700154721145799</v>
+        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2747902811690834</v>
       </c>
       <c r="AB4">
-        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3753360623896114</v>
+        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.277067223642631</v>
       </c>
       <c r="AC4">
-        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3800138681167788</v>
+        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2785593661591077</v>
       </c>
       <c r="AD4">
-        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3839996727107149</v>
+        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2794472919117685</v>
       </c>
       <c r="AE4">
-        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3872070048346188</v>
+        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2796273844678205</v>
       </c>
       <c r="AF4">
-        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3896847383062092</v>
-      </c>
-      <c r="AG4">
-        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3913084646411555</v>
-      </c>
-      <c r="AH4">
-        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392274691668502</v>
-      </c>
-      <c r="AI4">
-        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392470665593754</v>
-      </c>
-      <c r="AJ4">
-        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3919192618611231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38">
+        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2791206654872296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
       <c r="A5" t="s">
         <v>61</v>
       </c>
       <c r="B5">
-        <f>'Lawrence''s projections'!N$21/'Lawrence''s projections'!$N$21</f>
+        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$R$21</f>
         <v>1</v>
       </c>
       <c r="C5">
-        <f>'Lawrence''s projections'!O$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0227053788099791</v>
+        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0185734972871554</v>
       </c>
       <c r="D5">
-        <f>'Lawrence''s projections'!P$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0452319067405111</v>
+        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0366094241084758</v>
       </c>
       <c r="E5">
-        <f>'Lawrence''s projections'!Q$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0668176091706185</v>
+        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0540381204293101</v>
       </c>
       <c r="F5">
-        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0881844844019679</v>
+        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0704910645018531</v>
       </c>
       <c r="G5">
-        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1083958759709325</v>
+        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0862172536972476</v>
       </c>
       <c r="H5">
-        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1280222916997029</v>
+        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1010910619100174</v>
       </c>
       <c r="I5">
-        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1469879286193883</v>
+        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1153205331525904</v>
       </c>
       <c r="J5">
-        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1648917670818628</v>
+        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1292985133114011</v>
       </c>
       <c r="K5">
-        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1820047621630612</v>
+        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1428470896719243</v>
       </c>
       <c r="L5">
-        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1981902094841677</v>
+        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1557680882483976</v>
       </c>
       <c r="M5">
-        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2136744993115798</v>
+        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1681927379592973</v>
       </c>
       <c r="N5">
-        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2288851204436759</v>
+        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1801572515255192</v>
       </c>
       <c r="O5">
-        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2436284710249326</v>
+        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1917550324649424</v>
       </c>
       <c r="P5">
-        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2576889011988308</v>
+        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2027556833967945</v>
       </c>
       <c r="Q5">
-        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2712092122383614</v>
+        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2130009951676641</v>
       </c>
       <c r="R5">
-        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2842288102645407</v>
+        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2225748016844051</v>
       </c>
       <c r="S5">
-        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.296849335536314</v>
+        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2314569249479494</v>
       </c>
       <c r="T5">
-        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3088200731986774</v>
+        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2395815736087508</v>
       </c>
       <c r="U5">
-        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3199688625055988</v>
+        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2468376869604936</v>
       </c>
       <c r="V5">
-        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3303869302137827</v>
+        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2533299712929726</v>
       </c>
       <c r="W5">
-        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3400523189377174</v>
+        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2589919188817484</v>
       </c>
       <c r="X5">
-        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3488934355516187</v>
+        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2638813382323244</v>
       </c>
       <c r="Y5">
-        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.356789425518047</v>
+        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2681800631215496</v>
       </c>
       <c r="Z5">
-        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3638542285969768</v>
+        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2718428653863023</v>
       </c>
       <c r="AA5">
-        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3700154721145799</v>
+        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2747902811690834</v>
       </c>
       <c r="AB5">
-        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3753360623896114</v>
+        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.277067223642631</v>
       </c>
       <c r="AC5">
-        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3800138681167788</v>
+        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2785593661591077</v>
       </c>
       <c r="AD5">
-        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3839996727107149</v>
+        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2794472919117685</v>
       </c>
       <c r="AE5">
-        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3872070048346188</v>
+        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2796273844678205</v>
       </c>
       <c r="AF5">
-        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3896847383062092</v>
-      </c>
-      <c r="AG5">
-        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3913084646411555</v>
-      </c>
-      <c r="AH5">
-        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392274691668502</v>
-      </c>
-      <c r="AI5">
-        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392470665593754</v>
-      </c>
-      <c r="AJ5">
-        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3919192618611231</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38">
+        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2791206654872296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34">
       <c r="A6" t="s">
         <v>62</v>
       </c>
       <c r="B6">
-        <f>'Lawrence''s projections'!N$21/'Lawrence''s projections'!$N$21</f>
+        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$R$21</f>
         <v>1</v>
       </c>
       <c r="C6">
-        <f>'Lawrence''s projections'!O$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0227053788099791</v>
+        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0185734972871554</v>
       </c>
       <c r="D6">
-        <f>'Lawrence''s projections'!P$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0452319067405111</v>
+        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0366094241084758</v>
       </c>
       <c r="E6">
-        <f>'Lawrence''s projections'!Q$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0668176091706185</v>
+        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0540381204293101</v>
       </c>
       <c r="F6">
-        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0881844844019679</v>
+        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0704910645018531</v>
       </c>
       <c r="G6">
-        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1083958759709325</v>
+        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0862172536972476</v>
       </c>
       <c r="H6">
-        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1280222916997029</v>
+        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1010910619100174</v>
       </c>
       <c r="I6">
-        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1469879286193883</v>
+        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1153205331525904</v>
       </c>
       <c r="J6">
-        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1648917670818628</v>
+        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1292985133114011</v>
       </c>
       <c r="K6">
-        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1820047621630612</v>
+        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1428470896719243</v>
       </c>
       <c r="L6">
-        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1981902094841677</v>
+        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1557680882483976</v>
       </c>
       <c r="M6">
-        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2136744993115798</v>
+        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1681927379592973</v>
       </c>
       <c r="N6">
-        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2288851204436759</v>
+        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1801572515255192</v>
       </c>
       <c r="O6">
-        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2436284710249326</v>
+        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1917550324649424</v>
       </c>
       <c r="P6">
-        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2576889011988308</v>
+        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2027556833967945</v>
       </c>
       <c r="Q6">
-        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2712092122383614</v>
+        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2130009951676641</v>
       </c>
       <c r="R6">
-        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2842288102645407</v>
+        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2225748016844051</v>
       </c>
       <c r="S6">
-        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.296849335536314</v>
+        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2314569249479494</v>
       </c>
       <c r="T6">
-        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3088200731986774</v>
+        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2395815736087508</v>
       </c>
       <c r="U6">
-        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3199688625055988</v>
+        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2468376869604936</v>
       </c>
       <c r="V6">
-        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3303869302137827</v>
+        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2533299712929726</v>
       </c>
       <c r="W6">
-        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3400523189377174</v>
+        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2589919188817484</v>
       </c>
       <c r="X6">
-        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3488934355516187</v>
+        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2638813382323244</v>
       </c>
       <c r="Y6">
-        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.356789425518047</v>
+        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2681800631215496</v>
       </c>
       <c r="Z6">
-        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3638542285969768</v>
+        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2718428653863023</v>
       </c>
       <c r="AA6">
-        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3700154721145799</v>
+        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2747902811690834</v>
       </c>
       <c r="AB6">
-        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3753360623896114</v>
+        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.277067223642631</v>
       </c>
       <c r="AC6">
-        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3800138681167788</v>
+        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2785593661591077</v>
       </c>
       <c r="AD6">
-        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3839996727107149</v>
+        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2794472919117685</v>
       </c>
       <c r="AE6">
-        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3872070048346188</v>
+        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2796273844678205</v>
       </c>
       <c r="AF6">
-        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3896847383062092</v>
-      </c>
-      <c r="AG6">
-        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3913084646411555</v>
-      </c>
-      <c r="AH6">
-        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392274691668502</v>
-      </c>
-      <c r="AI6">
-        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392470665593754</v>
-      </c>
-      <c r="AJ6">
-        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3919192618611231</v>
-      </c>
-    </row>
-    <row r="7" spans="1:38">
+        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2791206654872296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
       <c r="A7" t="s">
         <v>63</v>
       </c>
       <c r="B7">
-        <f>'Lawrence''s projections'!N$21/'Lawrence''s projections'!$N$21</f>
+        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$R$21</f>
         <v>1</v>
       </c>
       <c r="C7">
-        <f>'Lawrence''s projections'!O$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0227053788099791</v>
+        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0185734972871554</v>
       </c>
       <c r="D7">
-        <f>'Lawrence''s projections'!P$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0452319067405111</v>
+        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0366094241084758</v>
       </c>
       <c r="E7">
-        <f>'Lawrence''s projections'!Q$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0668176091706185</v>
+        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0540381204293101</v>
       </c>
       <c r="F7">
-        <f>'Lawrence''s projections'!R$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.0881844844019679</v>
+        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0704910645018531</v>
       </c>
       <c r="G7">
-        <f>'Lawrence''s projections'!S$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1083958759709325</v>
+        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.0862172536972476</v>
       </c>
       <c r="H7">
-        <f>'Lawrence''s projections'!T$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1280222916997029</v>
+        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1010910619100174</v>
       </c>
       <c r="I7">
-        <f>'Lawrence''s projections'!U$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1469879286193883</v>
+        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1153205331525904</v>
       </c>
       <c r="J7">
-        <f>'Lawrence''s projections'!V$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1648917670818628</v>
+        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1292985133114011</v>
       </c>
       <c r="K7">
-        <f>'Lawrence''s projections'!W$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1820047621630612</v>
+        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1428470896719243</v>
       </c>
       <c r="L7">
-        <f>'Lawrence''s projections'!X$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.1981902094841677</v>
+        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1557680882483976</v>
       </c>
       <c r="M7">
-        <f>'Lawrence''s projections'!Y$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2136744993115798</v>
+        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1681927379592973</v>
       </c>
       <c r="N7">
-        <f>'Lawrence''s projections'!Z$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2288851204436759</v>
+        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1801572515255192</v>
       </c>
       <c r="O7">
-        <f>'Lawrence''s projections'!AA$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2436284710249326</v>
+        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.1917550324649424</v>
       </c>
       <c r="P7">
-        <f>'Lawrence''s projections'!AB$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2576889011988308</v>
+        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2027556833967945</v>
       </c>
       <c r="Q7">
-        <f>'Lawrence''s projections'!AC$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2712092122383614</v>
+        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2130009951676641</v>
       </c>
       <c r="R7">
-        <f>'Lawrence''s projections'!AD$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.2842288102645407</v>
+        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2225748016844051</v>
       </c>
       <c r="S7">
-        <f>'Lawrence''s projections'!AE$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.296849335536314</v>
+        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2314569249479494</v>
       </c>
       <c r="T7">
-        <f>'Lawrence''s projections'!AF$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3088200731986774</v>
+        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2395815736087508</v>
       </c>
       <c r="U7">
-        <f>'Lawrence''s projections'!AG$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3199688625055988</v>
+        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2468376869604936</v>
       </c>
       <c r="V7">
-        <f>'Lawrence''s projections'!AH$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3303869302137827</v>
+        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2533299712929726</v>
       </c>
       <c r="W7">
-        <f>'Lawrence''s projections'!AI$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3400523189377174</v>
+        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2589919188817484</v>
       </c>
       <c r="X7">
-        <f>'Lawrence''s projections'!AJ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3488934355516187</v>
+        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2638813382323244</v>
       </c>
       <c r="Y7">
-        <f>'Lawrence''s projections'!AK$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.356789425518047</v>
+        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2681800631215496</v>
       </c>
       <c r="Z7">
-        <f>'Lawrence''s projections'!AL$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3638542285969768</v>
+        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2718428653863023</v>
       </c>
       <c r="AA7">
-        <f>'Lawrence''s projections'!AM$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3700154721145799</v>
+        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2747902811690834</v>
       </c>
       <c r="AB7">
-        <f>'Lawrence''s projections'!AN$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3753360623896114</v>
+        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.277067223642631</v>
       </c>
       <c r="AC7">
-        <f>'Lawrence''s projections'!AO$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3800138681167788</v>
+        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2785593661591077</v>
       </c>
       <c r="AD7">
-        <f>'Lawrence''s projections'!AP$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3839996727107149</v>
+        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2794472919117685</v>
       </c>
       <c r="AE7">
-        <f>'Lawrence''s projections'!AQ$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3872070048346188</v>
+        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2796273844678205</v>
       </c>
       <c r="AF7">
-        <f>'Lawrence''s projections'!AR$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3896847383062092</v>
-      </c>
-      <c r="AG7">
-        <f>'Lawrence''s projections'!AS$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3913084646411555</v>
-      </c>
-      <c r="AH7">
-        <f>'Lawrence''s projections'!AT$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392274691668502</v>
-      </c>
-      <c r="AI7">
-        <f>'Lawrence''s projections'!AU$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.392470665593754</v>
-      </c>
-      <c r="AJ7">
-        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$N$21</f>
-        <v>1.3919192618611231</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38">
-      <c r="L8" s="8"/>
-    </row>
-    <row r="12" spans="1:38">
-      <c r="AL12" s="8"/>
-    </row>
-    <row r="14" spans="1:38">
-      <c r="F14" s="9"/>
+        <f>'Lawrence''s projections'!AV$21/'Lawrence''s projections'!$R$21</f>
+        <v>1.2791206654872296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="H8" s="8"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="AH12" s="8"/>
+    </row>
+    <row r="14" spans="1:34">
+      <c r="B14" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6904,1013 +6777,913 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AF7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="18" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" customWidth="1"/>
+    <col min="4" max="14" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
-      <c r="B1">
-        <v>2016</v>
-      </c>
-      <c r="C1">
-        <v>2017</v>
+    <row r="1" spans="1:32">
+      <c r="B1" s="9">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="9">
+        <v>2021</v>
       </c>
       <c r="D1" s="9">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="E1" s="9">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="F1" s="9">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G1" s="9">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="H1" s="9">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="I1" s="9">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="J1" s="9">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="K1" s="9">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="L1" s="9">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="M1" s="9">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="N1" s="9">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="O1" s="9">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="P1" s="9">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="Q1" s="9">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="R1" s="9">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="S1" s="9">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="T1" s="9">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="U1" s="9">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="V1" s="9">
-        <v>2036</v>
+        <v>2040</v>
       </c>
       <c r="W1" s="9">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="X1" s="9">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="Y1" s="9">
-        <v>2039</v>
+        <v>2043</v>
       </c>
       <c r="Z1" s="9">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="AA1" s="9">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="AB1" s="9">
-        <v>2042</v>
+        <v>2046</v>
       </c>
       <c r="AC1" s="9">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="AD1" s="9">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="AE1" s="9">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="AF1" s="9">
-        <v>2046</v>
-      </c>
-      <c r="AG1" s="9">
-        <v>2047</v>
-      </c>
-      <c r="AH1" s="9">
-        <v>2048</v>
-      </c>
-      <c r="AI1" s="9">
-        <v>2049</v>
-      </c>
-      <c r="AJ1" s="9">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>58</v>
       </c>
       <c r="B2">
-        <f>'Lawrence''s projections'!AC$78/'Lawrence''s projections'!$AC$78</f>
+        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AG$78</f>
         <v>1</v>
       </c>
       <c r="C2">
-        <f>'Lawrence''s projections'!AD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0094319399785638</v>
+        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.002784608366819</v>
       </c>
       <c r="D2">
-        <f>'Lawrence''s projections'!AE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.035145314632141</v>
+        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0074456408795787</v>
       </c>
       <c r="E2">
-        <f>'Lawrence''s projections'!AF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0392985925314497</v>
+        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0105975869831363</v>
       </c>
       <c r="F2">
-        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0433407713728955</v>
+        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0136858529591031</v>
       </c>
       <c r="G2">
-        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0462460668143039</v>
+        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0167128265119698</v>
       </c>
       <c r="H2">
-        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0511091120715605</v>
+        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0191794766461104</v>
       </c>
       <c r="I2">
-        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0543976659505723</v>
+        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.022208704668915</v>
       </c>
       <c r="J2">
-        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0576197797561422</v>
+        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0247025907033864</v>
       </c>
       <c r="K2">
-        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0607779446777155</v>
+        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0271638056522994</v>
       </c>
       <c r="L2">
-        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0633515013313768</v>
+        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0295936387004547</v>
       </c>
       <c r="M2">
-        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0665120184333541</v>
+        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0318811921465063</v>
       </c>
       <c r="N2">
-        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0691139914122756</v>
+        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0343641839285631</v>
       </c>
       <c r="O2">
-        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0716818773155889</v>
+        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0367073446447002</v>
       </c>
       <c r="P2">
-        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0742170212023587</v>
+        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0390240218755376</v>
       </c>
       <c r="Q2">
-        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0766037189793187</v>
+        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0413153790025276</v>
       </c>
       <c r="R2">
-        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0791943255405225</v>
+        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0437603111380687</v>
       </c>
       <c r="S2">
-        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0816390406495475</v>
+        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0458266710847399</v>
       </c>
       <c r="T2">
-        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0840561244585916</v>
+        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0480488192551356</v>
       </c>
       <c r="U2">
-        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0864467907709561</v>
+        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0502500749439818</v>
       </c>
       <c r="V2">
-        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0889976881512058</v>
+        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0527680109854669</v>
       </c>
       <c r="W2">
-        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0911536057319</v>
+        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0545941022636245</v>
       </c>
       <c r="X2">
-        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0934720635181054</v>
+        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0567389204997224</v>
       </c>
       <c r="Y2">
-        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0957687233264952</v>
+        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0588669405488367</v>
       </c>
       <c r="Z2">
-        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.098395788658286</v>
+        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0609791380423994</v>
       </c>
       <c r="AA2">
-        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1003010241410363</v>
+        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0630764704751499</v>
       </c>
       <c r="AB2">
-        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1025388004539414</v>
+        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0651598777040845</v>
       </c>
       <c r="AC2">
-        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1047590505334812</v>
+        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0672302824358038</v>
       </c>
       <c r="AD2">
-        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1069627922957068</v>
+        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0692885907025445</v>
       </c>
       <c r="AE2">
-        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.109151024733918</v>
+        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0713356923271764</v>
       </c>
       <c r="AF2">
-        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1113247284392385</v>
-      </c>
-      <c r="AG2">
-        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1134848661090846</v>
-      </c>
-      <c r="AH2">
-        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1156323830438288</v>
-      </c>
-      <c r="AI2">
-        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1177682076319513</v>
-      </c>
-      <c r="AJ2">
-        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1198932518239673</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36">
+        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0733724613774454</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>59</v>
       </c>
       <c r="B3">
-        <f>'Lawrence''s projections'!AC$78/'Lawrence''s projections'!$AC$78</f>
+        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AG$78</f>
         <v>1</v>
       </c>
       <c r="C3">
-        <f>'Lawrence''s projections'!AD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0094319399785638</v>
+        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.002784608366819</v>
       </c>
       <c r="D3">
-        <f>'Lawrence''s projections'!AE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.035145314632141</v>
+        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0074456408795787</v>
       </c>
       <c r="E3">
-        <f>'Lawrence''s projections'!AF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0392985925314497</v>
+        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0105975869831363</v>
       </c>
       <c r="F3">
-        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0433407713728955</v>
+        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0136858529591031</v>
       </c>
       <c r="G3">
-        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0462460668143039</v>
+        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0167128265119698</v>
       </c>
       <c r="H3">
-        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0511091120715605</v>
+        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0191794766461104</v>
       </c>
       <c r="I3">
-        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0543976659505723</v>
+        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.022208704668915</v>
       </c>
       <c r="J3">
-        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0576197797561422</v>
+        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0247025907033864</v>
       </c>
       <c r="K3">
-        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0607779446777155</v>
+        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0271638056522994</v>
       </c>
       <c r="L3">
-        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0633515013313768</v>
+        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0295936387004547</v>
       </c>
       <c r="M3">
-        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0665120184333541</v>
+        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0318811921465063</v>
       </c>
       <c r="N3">
-        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0691139914122756</v>
+        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0343641839285631</v>
       </c>
       <c r="O3">
-        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0716818773155889</v>
+        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0367073446447002</v>
       </c>
       <c r="P3">
-        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0742170212023587</v>
+        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0390240218755376</v>
       </c>
       <c r="Q3">
-        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0766037189793187</v>
+        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0413153790025276</v>
       </c>
       <c r="R3">
-        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0791943255405225</v>
+        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0437603111380687</v>
       </c>
       <c r="S3">
-        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0816390406495475</v>
+        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0458266710847399</v>
       </c>
       <c r="T3">
-        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0840561244585916</v>
+        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0480488192551356</v>
       </c>
       <c r="U3">
-        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0864467907709561</v>
+        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0502500749439818</v>
       </c>
       <c r="V3">
-        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0889976881512058</v>
+        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0527680109854669</v>
       </c>
       <c r="W3">
-        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0911536057319</v>
+        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0545941022636245</v>
       </c>
       <c r="X3">
-        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0934720635181054</v>
+        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0567389204997224</v>
       </c>
       <c r="Y3">
-        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0957687233264952</v>
+        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0588669405488367</v>
       </c>
       <c r="Z3">
-        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.098395788658286</v>
+        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0609791380423994</v>
       </c>
       <c r="AA3">
-        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1003010241410363</v>
+        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0630764704751499</v>
       </c>
       <c r="AB3">
-        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1025388004539414</v>
+        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0651598777040845</v>
       </c>
       <c r="AC3">
-        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1047590505334812</v>
+        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0672302824358038</v>
       </c>
       <c r="AD3">
-        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1069627922957068</v>
+        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0692885907025445</v>
       </c>
       <c r="AE3">
-        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.109151024733918</v>
+        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0713356923271764</v>
       </c>
       <c r="AF3">
-        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1113247284392385</v>
-      </c>
-      <c r="AG3">
-        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1134848661090846</v>
-      </c>
-      <c r="AH3">
-        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1156323830438288</v>
-      </c>
-      <c r="AI3">
-        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1177682076319513</v>
-      </c>
-      <c r="AJ3">
-        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1198932518239673</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36">
+        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0733724613774454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>60</v>
       </c>
       <c r="B4">
-        <f>'Lawrence''s projections'!AC$78/'Lawrence''s projections'!$AC$78</f>
+        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AG$78</f>
         <v>1</v>
       </c>
       <c r="C4">
-        <f>'Lawrence''s projections'!AD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0094319399785638</v>
+        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.002784608366819</v>
       </c>
       <c r="D4">
-        <f>'Lawrence''s projections'!AE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.035145314632141</v>
+        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0074456408795787</v>
       </c>
       <c r="E4">
-        <f>'Lawrence''s projections'!AF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0392985925314497</v>
+        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0105975869831363</v>
       </c>
       <c r="F4">
-        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0433407713728955</v>
+        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0136858529591031</v>
       </c>
       <c r="G4">
-        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0462460668143039</v>
+        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0167128265119698</v>
       </c>
       <c r="H4">
-        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0511091120715605</v>
+        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0191794766461104</v>
       </c>
       <c r="I4">
-        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0543976659505723</v>
+        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.022208704668915</v>
       </c>
       <c r="J4">
-        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0576197797561422</v>
+        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0247025907033864</v>
       </c>
       <c r="K4">
-        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0607779446777155</v>
+        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0271638056522994</v>
       </c>
       <c r="L4">
-        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0633515013313768</v>
+        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0295936387004547</v>
       </c>
       <c r="M4">
-        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0665120184333541</v>
+        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0318811921465063</v>
       </c>
       <c r="N4">
-        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0691139914122756</v>
+        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0343641839285631</v>
       </c>
       <c r="O4">
-        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0716818773155889</v>
+        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0367073446447002</v>
       </c>
       <c r="P4">
-        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0742170212023587</v>
+        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0390240218755376</v>
       </c>
       <c r="Q4">
-        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0766037189793187</v>
+        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0413153790025276</v>
       </c>
       <c r="R4">
-        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0791943255405225</v>
+        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0437603111380687</v>
       </c>
       <c r="S4">
-        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0816390406495475</v>
+        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0458266710847399</v>
       </c>
       <c r="T4">
-        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0840561244585916</v>
+        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0480488192551356</v>
       </c>
       <c r="U4">
-        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0864467907709561</v>
+        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0502500749439818</v>
       </c>
       <c r="V4">
-        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0889976881512058</v>
+        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0527680109854669</v>
       </c>
       <c r="W4">
-        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0911536057319</v>
+        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0545941022636245</v>
       </c>
       <c r="X4">
-        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0934720635181054</v>
+        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0567389204997224</v>
       </c>
       <c r="Y4">
-        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0957687233264952</v>
+        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0588669405488367</v>
       </c>
       <c r="Z4">
-        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.098395788658286</v>
+        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0609791380423994</v>
       </c>
       <c r="AA4">
-        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1003010241410363</v>
+        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0630764704751499</v>
       </c>
       <c r="AB4">
-        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1025388004539414</v>
+        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0651598777040845</v>
       </c>
       <c r="AC4">
-        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1047590505334812</v>
+        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0672302824358038</v>
       </c>
       <c r="AD4">
-        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1069627922957068</v>
+        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0692885907025445</v>
       </c>
       <c r="AE4">
-        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.109151024733918</v>
+        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0713356923271764</v>
       </c>
       <c r="AF4">
-        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1113247284392385</v>
-      </c>
-      <c r="AG4">
-        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1134848661090846</v>
-      </c>
-      <c r="AH4">
-        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1156323830438288</v>
-      </c>
-      <c r="AI4">
-        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1177682076319513</v>
-      </c>
-      <c r="AJ4">
-        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1198932518239673</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36">
+        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0733724613774454</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>61</v>
       </c>
       <c r="B5">
-        <f>'Lawrence''s projections'!AC$78/'Lawrence''s projections'!$AC$78</f>
+        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AG$78</f>
         <v>1</v>
       </c>
       <c r="C5">
-        <f>'Lawrence''s projections'!AD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0094319399785638</v>
+        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.002784608366819</v>
       </c>
       <c r="D5">
-        <f>'Lawrence''s projections'!AE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.035145314632141</v>
+        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0074456408795787</v>
       </c>
       <c r="E5">
-        <f>'Lawrence''s projections'!AF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0392985925314497</v>
+        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0105975869831363</v>
       </c>
       <c r="F5">
-        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0433407713728955</v>
+        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0136858529591031</v>
       </c>
       <c r="G5">
-        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0462460668143039</v>
+        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0167128265119698</v>
       </c>
       <c r="H5">
-        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0511091120715605</v>
+        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0191794766461104</v>
       </c>
       <c r="I5">
-        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0543976659505723</v>
+        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.022208704668915</v>
       </c>
       <c r="J5">
-        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0576197797561422</v>
+        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0247025907033864</v>
       </c>
       <c r="K5">
-        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0607779446777155</v>
+        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0271638056522994</v>
       </c>
       <c r="L5">
-        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0633515013313768</v>
+        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0295936387004547</v>
       </c>
       <c r="M5">
-        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0665120184333541</v>
+        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0318811921465063</v>
       </c>
       <c r="N5">
-        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0691139914122756</v>
+        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0343641839285631</v>
       </c>
       <c r="O5">
-        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0716818773155889</v>
+        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0367073446447002</v>
       </c>
       <c r="P5">
-        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0742170212023587</v>
+        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0390240218755376</v>
       </c>
       <c r="Q5">
-        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0766037189793187</v>
+        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0413153790025276</v>
       </c>
       <c r="R5">
-        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0791943255405225</v>
+        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0437603111380687</v>
       </c>
       <c r="S5">
-        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0816390406495475</v>
+        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0458266710847399</v>
       </c>
       <c r="T5">
-        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0840561244585916</v>
+        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0480488192551356</v>
       </c>
       <c r="U5">
-        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0864467907709561</v>
+        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0502500749439818</v>
       </c>
       <c r="V5">
-        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0889976881512058</v>
+        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0527680109854669</v>
       </c>
       <c r="W5">
-        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0911536057319</v>
+        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0545941022636245</v>
       </c>
       <c r="X5">
-        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0934720635181054</v>
+        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0567389204997224</v>
       </c>
       <c r="Y5">
-        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0957687233264952</v>
+        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0588669405488367</v>
       </c>
       <c r="Z5">
-        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.098395788658286</v>
+        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0609791380423994</v>
       </c>
       <c r="AA5">
-        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1003010241410363</v>
+        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0630764704751499</v>
       </c>
       <c r="AB5">
-        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1025388004539414</v>
+        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0651598777040845</v>
       </c>
       <c r="AC5">
-        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1047590505334812</v>
+        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0672302824358038</v>
       </c>
       <c r="AD5">
-        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1069627922957068</v>
+        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0692885907025445</v>
       </c>
       <c r="AE5">
-        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.109151024733918</v>
+        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0713356923271764</v>
       </c>
       <c r="AF5">
-        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1113247284392385</v>
-      </c>
-      <c r="AG5">
-        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1134848661090846</v>
-      </c>
-      <c r="AH5">
-        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1156323830438288</v>
-      </c>
-      <c r="AI5">
-        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1177682076319513</v>
-      </c>
-      <c r="AJ5">
-        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1198932518239673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36">
+        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0733724613774454</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>62</v>
       </c>
       <c r="B6">
-        <f>'Lawrence''s projections'!AC$78/'Lawrence''s projections'!$AC$78</f>
+        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AG$78</f>
         <v>1</v>
       </c>
       <c r="C6">
-        <f>'Lawrence''s projections'!AD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0094319399785638</v>
+        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.002784608366819</v>
       </c>
       <c r="D6">
-        <f>'Lawrence''s projections'!AE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.035145314632141</v>
+        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0074456408795787</v>
       </c>
       <c r="E6">
-        <f>'Lawrence''s projections'!AF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0392985925314497</v>
+        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0105975869831363</v>
       </c>
       <c r="F6">
-        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0433407713728955</v>
+        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0136858529591031</v>
       </c>
       <c r="G6">
-        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0462460668143039</v>
+        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0167128265119698</v>
       </c>
       <c r="H6">
-        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0511091120715605</v>
+        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0191794766461104</v>
       </c>
       <c r="I6">
-        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0543976659505723</v>
+        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.022208704668915</v>
       </c>
       <c r="J6">
-        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0576197797561422</v>
+        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0247025907033864</v>
       </c>
       <c r="K6">
-        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0607779446777155</v>
+        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0271638056522994</v>
       </c>
       <c r="L6">
-        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0633515013313768</v>
+        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0295936387004547</v>
       </c>
       <c r="M6">
-        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0665120184333541</v>
+        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0318811921465063</v>
       </c>
       <c r="N6">
-        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0691139914122756</v>
+        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0343641839285631</v>
       </c>
       <c r="O6">
-        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0716818773155889</v>
+        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0367073446447002</v>
       </c>
       <c r="P6">
-        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0742170212023587</v>
+        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0390240218755376</v>
       </c>
       <c r="Q6">
-        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0766037189793187</v>
+        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0413153790025276</v>
       </c>
       <c r="R6">
-        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0791943255405225</v>
+        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0437603111380687</v>
       </c>
       <c r="S6">
-        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0816390406495475</v>
+        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0458266710847399</v>
       </c>
       <c r="T6">
-        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0840561244585916</v>
+        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0480488192551356</v>
       </c>
       <c r="U6">
-        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0864467907709561</v>
+        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0502500749439818</v>
       </c>
       <c r="V6">
-        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0889976881512058</v>
+        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0527680109854669</v>
       </c>
       <c r="W6">
-        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0911536057319</v>
+        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0545941022636245</v>
       </c>
       <c r="X6">
-        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0934720635181054</v>
+        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0567389204997224</v>
       </c>
       <c r="Y6">
-        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0957687233264952</v>
+        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0588669405488367</v>
       </c>
       <c r="Z6">
-        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.098395788658286</v>
+        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0609791380423994</v>
       </c>
       <c r="AA6">
-        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1003010241410363</v>
+        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0630764704751499</v>
       </c>
       <c r="AB6">
-        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1025388004539414</v>
+        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0651598777040845</v>
       </c>
       <c r="AC6">
-        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1047590505334812</v>
+        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0672302824358038</v>
       </c>
       <c r="AD6">
-        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1069627922957068</v>
+        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0692885907025445</v>
       </c>
       <c r="AE6">
-        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.109151024733918</v>
+        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0713356923271764</v>
       </c>
       <c r="AF6">
-        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1113247284392385</v>
-      </c>
-      <c r="AG6">
-        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1134848661090846</v>
-      </c>
-      <c r="AH6">
-        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1156323830438288</v>
-      </c>
-      <c r="AI6">
-        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1177682076319513</v>
-      </c>
-      <c r="AJ6">
-        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1198932518239673</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36">
+        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0733724613774454</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>63</v>
       </c>
       <c r="B7">
-        <f>'Lawrence''s projections'!AC$78/'Lawrence''s projections'!$AC$78</f>
+        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AG$78</f>
         <v>1</v>
       </c>
       <c r="C7">
-        <f>'Lawrence''s projections'!AD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0094319399785638</v>
+        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.002784608366819</v>
       </c>
       <c r="D7">
-        <f>'Lawrence''s projections'!AE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.035145314632141</v>
+        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0074456408795787</v>
       </c>
       <c r="E7">
-        <f>'Lawrence''s projections'!AF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0392985925314497</v>
+        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0105975869831363</v>
       </c>
       <c r="F7">
-        <f>'Lawrence''s projections'!AG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0433407713728955</v>
+        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0136858529591031</v>
       </c>
       <c r="G7">
-        <f>'Lawrence''s projections'!AH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0462460668143039</v>
+        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0167128265119698</v>
       </c>
       <c r="H7">
-        <f>'Lawrence''s projections'!AI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0511091120715605</v>
+        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0191794766461104</v>
       </c>
       <c r="I7">
-        <f>'Lawrence''s projections'!AJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0543976659505723</v>
+        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.022208704668915</v>
       </c>
       <c r="J7">
-        <f>'Lawrence''s projections'!AK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0576197797561422</v>
+        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0247025907033864</v>
       </c>
       <c r="K7">
-        <f>'Lawrence''s projections'!AL$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0607779446777155</v>
+        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0271638056522994</v>
       </c>
       <c r="L7">
-        <f>'Lawrence''s projections'!AM$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0633515013313768</v>
+        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0295936387004547</v>
       </c>
       <c r="M7">
-        <f>'Lawrence''s projections'!AN$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0665120184333541</v>
+        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0318811921465063</v>
       </c>
       <c r="N7">
-        <f>'Lawrence''s projections'!AO$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0691139914122756</v>
+        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0343641839285631</v>
       </c>
       <c r="O7">
-        <f>'Lawrence''s projections'!AP$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0716818773155889</v>
+        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0367073446447002</v>
       </c>
       <c r="P7">
-        <f>'Lawrence''s projections'!AQ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0742170212023587</v>
+        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0390240218755376</v>
       </c>
       <c r="Q7">
-        <f>'Lawrence''s projections'!AR$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0766037189793187</v>
+        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0413153790025276</v>
       </c>
       <c r="R7">
-        <f>'Lawrence''s projections'!AS$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0791943255405225</v>
+        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0437603111380687</v>
       </c>
       <c r="S7">
-        <f>'Lawrence''s projections'!AT$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0816390406495475</v>
+        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0458266710847399</v>
       </c>
       <c r="T7">
-        <f>'Lawrence''s projections'!AU$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0840561244585916</v>
+        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0480488192551356</v>
       </c>
       <c r="U7">
-        <f>'Lawrence''s projections'!AV$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0864467907709561</v>
+        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0502500749439818</v>
       </c>
       <c r="V7">
-        <f>'Lawrence''s projections'!AW$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0889976881512058</v>
+        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0527680109854669</v>
       </c>
       <c r="W7">
-        <f>'Lawrence''s projections'!AX$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0911536057319</v>
+        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0545941022636245</v>
       </c>
       <c r="X7">
-        <f>'Lawrence''s projections'!AY$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0934720635181054</v>
+        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0567389204997224</v>
       </c>
       <c r="Y7">
-        <f>'Lawrence''s projections'!AZ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.0957687233264952</v>
+        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0588669405488367</v>
       </c>
       <c r="Z7">
-        <f>'Lawrence''s projections'!BA$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.098395788658286</v>
+        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0609791380423994</v>
       </c>
       <c r="AA7">
-        <f>'Lawrence''s projections'!BB$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1003010241410363</v>
+        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0630764704751499</v>
       </c>
       <c r="AB7">
-        <f>'Lawrence''s projections'!BC$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1025388004539414</v>
+        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0651598777040845</v>
       </c>
       <c r="AC7">
-        <f>'Lawrence''s projections'!BD$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1047590505334812</v>
+        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0672302824358038</v>
       </c>
       <c r="AD7">
-        <f>'Lawrence''s projections'!BE$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1069627922957068</v>
+        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0692885907025445</v>
       </c>
       <c r="AE7">
-        <f>'Lawrence''s projections'!BF$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.109151024733918</v>
+        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0713356923271764</v>
       </c>
       <c r="AF7">
-        <f>'Lawrence''s projections'!BG$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1113247284392385</v>
-      </c>
-      <c r="AG7">
-        <f>'Lawrence''s projections'!BH$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1134848661090846</v>
-      </c>
-      <c r="AH7">
-        <f>'Lawrence''s projections'!BI$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1156323830438288</v>
-      </c>
-      <c r="AI7">
-        <f>'Lawrence''s projections'!BJ$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1177682076319513</v>
-      </c>
-      <c r="AJ7">
-        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AC$78</f>
-        <v>1.1198932518239673</v>
+        <f>'Lawrence''s projections'!BK$78/'Lawrence''s projections'!$AG$78</f>
+        <v>1.0733724613774454</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8144,15 +7917,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8163,6 +7927,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDF5E3D-2090-4A5C-AE1D-CEA2430518B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95CB3B09-2058-42B8-B543-9FFC128D2595}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8178,14 +7950,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDF5E3D-2090-4A5C-AE1D-CEA2430518B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
